--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/45.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/45.xlsx
@@ -426,13 +426,13 @@
         <v>-5.707275823788772</v>
       </c>
       <c r="E2">
-        <v>-16.24263754946548</v>
+        <v>-22.83455602347091</v>
       </c>
       <c r="F2">
-        <v>-2.124769990734865</v>
+        <v>-3.878250653674233</v>
       </c>
       <c r="G2">
-        <v>-14.30016248537506</v>
+        <v>-16.24509143696919</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.516312617160647</v>
       </c>
       <c r="E3">
-        <v>-16.75759749972172</v>
+        <v>-23.28410216668636</v>
       </c>
       <c r="F3">
-        <v>-2.004456252417459</v>
+        <v>-3.489781961559586</v>
       </c>
       <c r="G3">
-        <v>-12.75373217670685</v>
+        <v>-16.33414014615727</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.393578123921368</v>
       </c>
       <c r="E4">
-        <v>-15.5591006257997</v>
+        <v>-23.10162730654728</v>
       </c>
       <c r="F4">
-        <v>-2.096834128442854</v>
+        <v>-3.207901788265358</v>
       </c>
       <c r="G4">
-        <v>-13.87432866793138</v>
+        <v>-16.55101398443493</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.350537822192583</v>
       </c>
       <c r="E5">
-        <v>-17.64095786744996</v>
+        <v>-24.15791651120643</v>
       </c>
       <c r="F5">
-        <v>-1.795578441597147</v>
+        <v>-3.204179105157178</v>
       </c>
       <c r="G5">
-        <v>-13.19403142288438</v>
+        <v>-15.70380565438896</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.375053421097553</v>
       </c>
       <c r="E6">
-        <v>-18.17559856574354</v>
+        <v>-24.29824939223013</v>
       </c>
       <c r="F6">
-        <v>-2.178120164944764</v>
+        <v>-3.238249028066918</v>
       </c>
       <c r="G6">
-        <v>-13.75637889618545</v>
+        <v>-15.67607321440648</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.456209998935076</v>
       </c>
       <c r="E7">
-        <v>-18.14605027284349</v>
+        <v>-24.51639957060163</v>
       </c>
       <c r="F7">
-        <v>-1.787677473309245</v>
+        <v>-3.35862655067434</v>
       </c>
       <c r="G7">
-        <v>-13.11763727402016</v>
+        <v>-15.23681016898275</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.572942038649629</v>
       </c>
       <c r="E8">
-        <v>-19.30888994242911</v>
+        <v>-25.96211036907638</v>
       </c>
       <c r="F8">
-        <v>-2.029403365120169</v>
+        <v>-3.306435262460957</v>
       </c>
       <c r="G8">
-        <v>-13.4220882839937</v>
+        <v>-15.19350492278354</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.714416703953044</v>
       </c>
       <c r="E9">
-        <v>-18.97612408692348</v>
+        <v>-25.33749794919841</v>
       </c>
       <c r="F9">
-        <v>-1.23122249884608</v>
+        <v>-3.277572457045214</v>
       </c>
       <c r="G9">
-        <v>-11.9215471023181</v>
+        <v>-14.88308168865716</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.864034218028451</v>
       </c>
       <c r="E10">
-        <v>-19.7937083696903</v>
+        <v>-26.42391509143059</v>
       </c>
       <c r="F10">
-        <v>-1.344872021407964</v>
+        <v>-3.031202737574196</v>
       </c>
       <c r="G10">
-        <v>-11.20316203084179</v>
+        <v>-14.99453120423672</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.005891674374179</v>
       </c>
       <c r="E11">
-        <v>-20.41763246151911</v>
+        <v>-26.73698661347687</v>
       </c>
       <c r="F11">
-        <v>-1.852253682561883</v>
+        <v>-3.069769038746332</v>
       </c>
       <c r="G11">
-        <v>-11.31010589394241</v>
+        <v>-14.3466822712929</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.125049775475977</v>
       </c>
       <c r="E12">
-        <v>-20.14431641278617</v>
+        <v>-27.68414865149918</v>
       </c>
       <c r="F12">
-        <v>-1.19896670054847</v>
+        <v>-2.946648791668242</v>
       </c>
       <c r="G12">
-        <v>-11.00658845781095</v>
+        <v>-14.27674203095749</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.204964525645363</v>
       </c>
       <c r="E13">
-        <v>-20.52617998348297</v>
+        <v>-27.50436370492066</v>
       </c>
       <c r="F13">
-        <v>-0.8995773254612701</v>
+        <v>-2.896366890318312</v>
       </c>
       <c r="G13">
-        <v>-11.36971557692252</v>
+        <v>-13.81690063446164</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.240864946815993</v>
       </c>
       <c r="E14">
-        <v>-21.13394648005241</v>
+        <v>-28.67170467766991</v>
       </c>
       <c r="F14">
-        <v>-0.6267793723713369</v>
+        <v>-3.035226118049593</v>
       </c>
       <c r="G14">
-        <v>-11.45021811280098</v>
+        <v>-13.75383143139298</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.22683596734927</v>
       </c>
       <c r="E15">
-        <v>-22.09573548911949</v>
+        <v>-28.8335840380221</v>
       </c>
       <c r="F15">
-        <v>-0.4458018040447149</v>
+        <v>-2.517687015802546</v>
       </c>
       <c r="G15">
-        <v>-11.38103764266683</v>
+        <v>-13.0067869671832</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.159275205218155</v>
       </c>
       <c r="E16">
-        <v>-23.02037289742765</v>
+        <v>-29.10992963586618</v>
       </c>
       <c r="F16">
-        <v>-0.1980081210082848</v>
+        <v>-2.329139826149142</v>
       </c>
       <c r="G16">
-        <v>-9.86130191795454</v>
+        <v>-13.06542666032031</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.037746576909074</v>
       </c>
       <c r="E17">
-        <v>-23.35297119939501</v>
+        <v>-30.20713133894763</v>
       </c>
       <c r="F17">
-        <v>0.1529554085772126</v>
+        <v>-2.351096532527746</v>
       </c>
       <c r="G17">
-        <v>-10.65205220437378</v>
+        <v>-12.24928117906933</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.861565070293161</v>
       </c>
       <c r="E18">
-        <v>-24.60805135604287</v>
+        <v>-30.17939443565064</v>
       </c>
       <c r="F18">
-        <v>-0.2169445998362815</v>
+        <v>-2.139959763799999</v>
       </c>
       <c r="G18">
-        <v>-10.65623342338988</v>
+        <v>-12.47453731865242</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.641416959906129</v>
       </c>
       <c r="E19">
-        <v>-25.57550095761954</v>
+        <v>-31.40762753414403</v>
       </c>
       <c r="F19">
-        <v>0.1334755207329794</v>
+        <v>-1.952935113432941</v>
       </c>
       <c r="G19">
-        <v>-9.325142515141874</v>
+        <v>-11.72967781449856</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.388054348986651</v>
       </c>
       <c r="E20">
-        <v>-26.26080851462232</v>
+        <v>-31.55579920367501</v>
       </c>
       <c r="F20">
-        <v>0.0935805182467524</v>
+        <v>-1.887936436804875</v>
       </c>
       <c r="G20">
-        <v>-8.99002592183807</v>
+        <v>-11.7403874293181</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.113097981752695</v>
       </c>
       <c r="E21">
-        <v>-27.33836343322149</v>
+        <v>-32.14258301592991</v>
       </c>
       <c r="F21">
-        <v>0.4842775186749308</v>
+        <v>-1.567962131758107</v>
       </c>
       <c r="G21">
-        <v>-8.384037181965558</v>
+        <v>-11.83670444123766</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.828088402776515</v>
       </c>
       <c r="E22">
-        <v>-26.00615883574899</v>
+        <v>-33.08589585104569</v>
       </c>
       <c r="F22">
-        <v>0.3271445060378926</v>
+        <v>-1.63833028589112</v>
       </c>
       <c r="G22">
-        <v>-9.006495885895944</v>
+        <v>-11.81567254542667</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.539806126589274</v>
       </c>
       <c r="E23">
-        <v>-28.27538621794062</v>
+        <v>-33.65848516152355</v>
       </c>
       <c r="F23">
-        <v>0.6429049061066193</v>
+        <v>-1.38898341397444</v>
       </c>
       <c r="G23">
-        <v>-8.271174063440725</v>
+        <v>-11.70954307652871</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.259881185504689</v>
       </c>
       <c r="E24">
-        <v>-26.72583298199598</v>
+        <v>-33.50260829346853</v>
       </c>
       <c r="F24">
-        <v>0.9026958342377946</v>
+        <v>-1.401007166826075</v>
       </c>
       <c r="G24">
-        <v>-8.512383721977562</v>
+        <v>-11.10064767767272</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.994552677953338</v>
       </c>
       <c r="E25">
-        <v>-28.48071175792241</v>
+        <v>-33.63464953858418</v>
       </c>
       <c r="F25">
-        <v>0.8236347925798043</v>
+        <v>-1.150028411125881</v>
       </c>
       <c r="G25">
-        <v>-8.87996021429392</v>
+        <v>-11.47107123915285</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.746805502598232</v>
       </c>
       <c r="E26">
-        <v>-28.34709460385209</v>
+        <v>-33.66552014589447</v>
       </c>
       <c r="F26">
-        <v>0.8942000981546829</v>
+        <v>-1.278166079562728</v>
       </c>
       <c r="G26">
-        <v>-8.70222364538153</v>
+        <v>-11.54010935582881</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.517456122986439</v>
       </c>
       <c r="E27">
-        <v>-28.80665320309849</v>
+        <v>-34.5057784980177</v>
       </c>
       <c r="F27">
-        <v>0.8662957138239789</v>
+        <v>-1.256341083601169</v>
       </c>
       <c r="G27">
-        <v>-7.377075166376519</v>
+        <v>-11.12877738311991</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.302842571871799</v>
       </c>
       <c r="E28">
-        <v>-27.81255806046068</v>
+        <v>-33.91189177428177</v>
       </c>
       <c r="F28">
-        <v>0.8965973934183847</v>
+        <v>-1.100448965333525</v>
       </c>
       <c r="G28">
-        <v>-7.575433123453031</v>
+        <v>-11.66353642516946</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.104459446527592</v>
       </c>
       <c r="E29">
-        <v>-29.77693083669295</v>
+        <v>-33.91044719107332</v>
       </c>
       <c r="F29">
-        <v>0.9838046001155055</v>
+        <v>-1.254466488168634</v>
       </c>
       <c r="G29">
-        <v>-9.102064714523625</v>
+        <v>-11.5259038049198</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.920812684709615</v>
       </c>
       <c r="E30">
-        <v>-28.01854022917358</v>
+        <v>-34.29156129932186</v>
       </c>
       <c r="F30">
-        <v>0.9156680677656349</v>
+        <v>-1.589160881963149</v>
       </c>
       <c r="G30">
-        <v>-7.17747906526832</v>
+        <v>-10.98026299968266</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.749333437301591</v>
       </c>
       <c r="E31">
-        <v>-28.91609283444186</v>
+        <v>-33.90360919532174</v>
       </c>
       <c r="F31">
-        <v>0.2880265121754915</v>
+        <v>-1.045357562842941</v>
       </c>
       <c r="G31">
-        <v>-8.495430418270955</v>
+        <v>-11.68689232394902</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.587713155483245</v>
       </c>
       <c r="E32">
-        <v>-28.64860946023079</v>
+        <v>-33.3114885764488</v>
       </c>
       <c r="F32">
-        <v>0.8235072239997732</v>
+        <v>-1.104564294590633</v>
       </c>
       <c r="G32">
-        <v>-7.286432429511274</v>
+        <v>-11.00818083021534</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.432251780781305</v>
       </c>
       <c r="E33">
-        <v>-29.33493139541129</v>
+        <v>-33.63860742486688</v>
       </c>
       <c r="F33">
-        <v>0.4352017202634769</v>
+        <v>-1.392299368687847</v>
       </c>
       <c r="G33">
-        <v>-7.716366357605344</v>
+        <v>-11.56793118054085</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.284267424474757</v>
       </c>
       <c r="E34">
-        <v>-27.35366514689341</v>
+        <v>-33.06705739917378</v>
       </c>
       <c r="F34">
-        <v>0.9454230248741932</v>
+        <v>-1.474698730979119</v>
       </c>
       <c r="G34">
-        <v>-7.862119746062837</v>
+        <v>-11.45107885464119</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.144023271277469</v>
       </c>
       <c r="E35">
-        <v>-27.74822203023371</v>
+        <v>-33.33309845441341</v>
       </c>
       <c r="F35">
-        <v>0.4040252846917147</v>
+        <v>-1.428973678711989</v>
       </c>
       <c r="G35">
-        <v>-7.51566122374149</v>
+        <v>-11.61298439478479</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.011421080993091</v>
       </c>
       <c r="E36">
-        <v>-26.80039430653227</v>
+        <v>-32.70668596611738</v>
       </c>
       <c r="F36">
-        <v>0.7735334753236845</v>
+        <v>-1.541989500210732</v>
       </c>
       <c r="G36">
-        <v>-7.3188393597952</v>
+        <v>-11.73298173894675</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.886721006678548</v>
       </c>
       <c r="E37">
-        <v>-26.72529409358907</v>
+        <v>-31.63389273793728</v>
       </c>
       <c r="F37">
-        <v>0.5682085322939795</v>
+        <v>-1.633034533085022</v>
       </c>
       <c r="G37">
-        <v>-7.439578266157959</v>
+        <v>-11.51352567514846</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.769268756176151</v>
       </c>
       <c r="E38">
-        <v>-26.15533129803566</v>
+        <v>-31.85137496639265</v>
       </c>
       <c r="F38">
-        <v>0.472604993602083</v>
+        <v>-1.634469265426671</v>
       </c>
       <c r="G38">
-        <v>-7.236112137314352</v>
+        <v>-11.65363789400704</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.661811150036252</v>
       </c>
       <c r="E39">
-        <v>-25.84594142535762</v>
+        <v>-31.43976611417647</v>
       </c>
       <c r="F39">
-        <v>0.6255969975925265</v>
+        <v>-1.368415879730331</v>
       </c>
       <c r="G39">
-        <v>-7.357996492433699</v>
+        <v>-10.95001454509034</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.566987467258208</v>
       </c>
       <c r="E40">
-        <v>-24.67302590110492</v>
+        <v>-30.84643412850648</v>
       </c>
       <c r="F40">
-        <v>0.5314530422643626</v>
+        <v>-1.378015001193972</v>
       </c>
       <c r="G40">
-        <v>-7.028355541451849</v>
+        <v>-11.31534979807661</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.487188433114368</v>
       </c>
       <c r="E41">
-        <v>-23.53795483413433</v>
+        <v>-30.44841975526132</v>
       </c>
       <c r="F41">
-        <v>0.3585769071371198</v>
+        <v>-1.356251304420221</v>
       </c>
       <c r="G41">
-        <v>-7.787175616144816</v>
+        <v>-11.29765162162367</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.425113013905591</v>
       </c>
       <c r="E42">
-        <v>-24.88052510861039</v>
+        <v>-30.07044840797411</v>
       </c>
       <c r="F42">
-        <v>0.722179666554532</v>
+        <v>-1.484784932475606</v>
       </c>
       <c r="G42">
-        <v>-7.490047532904148</v>
+        <v>-11.74043377695565</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.38209848688102</v>
       </c>
       <c r="E43">
-        <v>-23.09746111046022</v>
+        <v>-29.37274415337534</v>
       </c>
       <c r="F43">
-        <v>-0.4286728228896267</v>
+        <v>-1.194846401086946</v>
       </c>
       <c r="G43">
-        <v>-7.855644318988023</v>
+        <v>-10.93074717005178</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.36109698506005</v>
       </c>
       <c r="E44">
-        <v>-23.88950479982379</v>
+        <v>-29.43490878031563</v>
       </c>
       <c r="F44">
-        <v>0.4887324785671865</v>
+        <v>-1.54594826802871</v>
       </c>
       <c r="G44">
-        <v>-7.823058619244977</v>
+        <v>-11.53455426041391</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.364729783519709</v>
       </c>
       <c r="E45">
-        <v>-22.30027760309795</v>
+        <v>-28.98230818138201</v>
       </c>
       <c r="F45">
-        <v>-0.1473592528989146</v>
+        <v>-1.460039941419179</v>
       </c>
       <c r="G45">
-        <v>-7.519895411486218</v>
+        <v>-11.46443690589215</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.393881024857604</v>
       </c>
       <c r="E46">
-        <v>-22.52206867457162</v>
+        <v>-28.0749333159911</v>
       </c>
       <c r="F46">
-        <v>0.3951460145011068</v>
+        <v>-1.493562313475669</v>
       </c>
       <c r="G46">
-        <v>-8.170212356129571</v>
+        <v>-11.38830429012553</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.448857216805484</v>
       </c>
       <c r="E47">
-        <v>-23.3065633977644</v>
+        <v>-27.82889679468036</v>
       </c>
       <c r="F47">
-        <v>0.1239153325372703</v>
+        <v>-1.356737556085664</v>
       </c>
       <c r="G47">
-        <v>-7.818754910043924</v>
+        <v>-11.62973244466796</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.527815415587562</v>
       </c>
       <c r="E48">
-        <v>-20.84416942830158</v>
+        <v>-27.34318172956565</v>
       </c>
       <c r="F48">
-        <v>0.1105686769433647</v>
+        <v>-1.608576985517367</v>
       </c>
       <c r="G48">
-        <v>-7.911191962591454</v>
+        <v>-11.24668577304659</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.629253358823488</v>
       </c>
       <c r="E49">
-        <v>-22.08767480538584</v>
+        <v>-26.38562684369574</v>
       </c>
       <c r="F49">
-        <v>0.500737178968557</v>
+        <v>-1.637529254612612</v>
       </c>
       <c r="G49">
-        <v>-8.40183136423914</v>
+        <v>-11.09187473199365</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.752216919402169</v>
       </c>
       <c r="E50">
-        <v>-20.88766089267125</v>
+        <v>-26.78911840625317</v>
       </c>
       <c r="F50">
-        <v>-0.01752674475593969</v>
+        <v>-1.723034994664383</v>
       </c>
       <c r="G50">
-        <v>-8.206297302507627</v>
+        <v>-11.99295556960018</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.894297357034027</v>
       </c>
       <c r="E51">
-        <v>-19.90554809225774</v>
+        <v>-25.95675771279932</v>
       </c>
       <c r="F51">
-        <v>-0.0344353801818832</v>
+        <v>-1.66453817378089</v>
       </c>
       <c r="G51">
-        <v>-7.265072789691897</v>
+        <v>-11.86039139457114</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.053195533754708</v>
       </c>
       <c r="E52">
-        <v>-18.61519565156413</v>
+        <v>-26.02975218532896</v>
       </c>
       <c r="F52">
-        <v>0.1469696257245833</v>
+        <v>-1.721168682905876</v>
       </c>
       <c r="G52">
-        <v>-7.590916544940202</v>
+        <v>-11.44259392642404</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.225083854420659</v>
       </c>
       <c r="E53">
-        <v>-19.03930535627849</v>
+        <v>-25.52418429016462</v>
       </c>
       <c r="F53">
-        <v>0.1533116065604163</v>
+        <v>-1.455543563156783</v>
       </c>
       <c r="G53">
-        <v>-8.485240559101078</v>
+        <v>-11.9539606536931</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.406277435886739</v>
       </c>
       <c r="E54">
-        <v>-18.99871664374774</v>
+        <v>-25.36306571344572</v>
       </c>
       <c r="F54">
-        <v>0.04272704338889075</v>
+        <v>-1.67004184680509</v>
       </c>
       <c r="G54">
-        <v>-7.956096202286129</v>
+        <v>-11.82755740391265</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.594818147487384</v>
       </c>
       <c r="E55">
-        <v>-19.81670396070125</v>
+        <v>-25.1221191969196</v>
       </c>
       <c r="F55">
-        <v>0.3919849644920239</v>
+        <v>-1.59477721295413</v>
       </c>
       <c r="G55">
-        <v>-8.06610232001057</v>
+        <v>-12.10008813379653</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.787374481749996</v>
       </c>
       <c r="E56">
-        <v>-19.11122658046831</v>
+        <v>-24.83386824090936</v>
       </c>
       <c r="F56">
-        <v>-0.5903717966508958</v>
+        <v>-1.462607880367858</v>
       </c>
       <c r="G56">
-        <v>-8.586288340596253</v>
+        <v>-12.22277033039084</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.98078340969978</v>
       </c>
       <c r="E57">
-        <v>-17.89233345961575</v>
+        <v>-24.56033935389805</v>
       </c>
       <c r="F57">
-        <v>-0.133913193216673</v>
+        <v>-1.464496558046241</v>
       </c>
       <c r="G57">
-        <v>-8.569636296533718</v>
+        <v>-12.01829448515776</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.170865785521534</v>
       </c>
       <c r="E58">
-        <v>-17.55866190930857</v>
+        <v>-23.65474417879215</v>
       </c>
       <c r="F58">
-        <v>0.2601544341734966</v>
+        <v>-1.841595079190062</v>
       </c>
       <c r="G58">
-        <v>-8.617794802493496</v>
+        <v>-12.53234606485917</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.353832664912147</v>
       </c>
       <c r="E59">
-        <v>-17.85861444215463</v>
+        <v>-23.63370036007851</v>
       </c>
       <c r="F59">
-        <v>-0.1829889916281269</v>
+        <v>-1.546398899895833</v>
       </c>
       <c r="G59">
-        <v>-7.923881283643481</v>
+        <v>-11.92697970754804</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.528872815431829</v>
       </c>
       <c r="E60">
-        <v>-16.41671661879434</v>
+        <v>-23.57807258536829</v>
       </c>
       <c r="F60">
-        <v>0.3573177886848646</v>
+        <v>-1.635662114486702</v>
       </c>
       <c r="G60">
-        <v>-8.216291839490687</v>
+        <v>-12.50030329458457</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.693493636186429</v>
       </c>
       <c r="E61">
-        <v>-16.87583595606199</v>
+        <v>-23.35310252514123</v>
       </c>
       <c r="F61">
-        <v>-0.2888477187666814</v>
+        <v>-1.526239750781304</v>
       </c>
       <c r="G61">
-        <v>-7.818778083862699</v>
+        <v>-12.12756235122695</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.844965526348895</v>
       </c>
       <c r="E62">
-        <v>-17.92830765713268</v>
+        <v>-23.47049868531608</v>
       </c>
       <c r="F62">
-        <v>-0.003473491767446079</v>
+        <v>-1.559597277724638</v>
       </c>
       <c r="G62">
-        <v>-8.796504671794434</v>
+        <v>-12.66499300352669</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.97896476580741</v>
       </c>
       <c r="E63">
-        <v>-16.94312455134197</v>
+        <v>-23.78009233932447</v>
       </c>
       <c r="F63">
-        <v>0.09739597850404692</v>
+        <v>-2.006608350929932</v>
       </c>
       <c r="G63">
-        <v>-8.635698232769874</v>
+        <v>-12.20450605065069</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.091377609265225</v>
       </c>
       <c r="E64">
-        <v>-16.53074359430747</v>
+        <v>-22.7056077261025</v>
       </c>
       <c r="F64">
-        <v>0.452839319003884</v>
+        <v>-1.603475070683525</v>
       </c>
       <c r="G64">
-        <v>-8.753338468507877</v>
+        <v>-12.39358454858062</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.181619316462838</v>
       </c>
       <c r="E65">
-        <v>-17.71885667732991</v>
+        <v>-22.38438947931642</v>
       </c>
       <c r="F65">
-        <v>-0.4222289528632494</v>
+        <v>-1.940997510791197</v>
       </c>
       <c r="G65">
-        <v>-9.066026115783119</v>
+        <v>-12.47822195583763</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.24768973019416</v>
       </c>
       <c r="E66">
-        <v>-17.11829951138068</v>
+        <v>-22.73792744509524</v>
       </c>
       <c r="F66">
-        <v>-0.2749609676261505</v>
+        <v>-1.867200743977998</v>
       </c>
       <c r="G66">
-        <v>-8.717087994852857</v>
+        <v>-12.74194994513259</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.288093194492431</v>
       </c>
       <c r="E67">
-        <v>-16.7156094887226</v>
+        <v>-23.03884907137894</v>
       </c>
       <c r="F67">
-        <v>0.0146611274146407</v>
+        <v>-2.147942740460778</v>
       </c>
       <c r="G67">
-        <v>-8.58457016746137</v>
+        <v>-12.78898948670009</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.301011933866726</v>
       </c>
       <c r="E68">
-        <v>-16.86498573233962</v>
+        <v>-22.66546733249851</v>
       </c>
       <c r="F68">
-        <v>-0.7087927154529047</v>
+        <v>-1.777344418326724</v>
       </c>
       <c r="G68">
-        <v>-8.658100694434124</v>
+        <v>-12.70420310489382</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.285773440700857</v>
       </c>
       <c r="E69">
-        <v>-16.16586632961344</v>
+        <v>-23.11047594475827</v>
       </c>
       <c r="F69">
-        <v>-0.143287827114155</v>
+        <v>-1.985736805848996</v>
       </c>
       <c r="G69">
-        <v>-8.46746624010073</v>
+        <v>-12.37573077648733</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.245731124755091</v>
       </c>
       <c r="E70">
-        <v>-17.03752059203186</v>
+        <v>-23.0231171526763</v>
       </c>
       <c r="F70">
-        <v>-0.4984528361666515</v>
+        <v>-1.802930202296993</v>
       </c>
       <c r="G70">
-        <v>-8.470664227091667</v>
+        <v>-11.91607477054168</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.182588423802251</v>
       </c>
       <c r="E71">
-        <v>-16.61939752995564</v>
+        <v>-22.39705562111587</v>
       </c>
       <c r="F71">
-        <v>-0.5224721773782259</v>
+        <v>-1.942166337196547</v>
       </c>
       <c r="G71">
-        <v>-8.220645206874828</v>
+        <v>-12.08436966357607</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.098012229059583</v>
       </c>
       <c r="E72">
-        <v>-15.70605866429662</v>
+        <v>-23.56883902686664</v>
       </c>
       <c r="F72">
-        <v>-0.5832552922934453</v>
+        <v>-2.07507540187352</v>
       </c>
       <c r="G72">
-        <v>-8.338623118257836</v>
+        <v>-12.06659203403019</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.992621385058558</v>
       </c>
       <c r="E73">
-        <v>-17.76631055645629</v>
+        <v>-23.08129898672685</v>
       </c>
       <c r="F73">
-        <v>-0.485167479760553</v>
+        <v>-2.150891728414745</v>
       </c>
       <c r="G73">
-        <v>-8.791111793110961</v>
+        <v>-12.31508489275342</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.867458394052235</v>
       </c>
       <c r="E74">
-        <v>-17.83240363459824</v>
+        <v>-22.916082141031</v>
       </c>
       <c r="F74">
-        <v>-0.8851695312243782</v>
+        <v>-2.32812424771331</v>
       </c>
       <c r="G74">
-        <v>-7.52251736355332</v>
+        <v>-12.07098181741526</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.726933831636258</v>
       </c>
       <c r="E75">
-        <v>-15.85934298098225</v>
+        <v>-23.03156728517461</v>
       </c>
       <c r="F75">
-        <v>-0.3557740063410618</v>
+        <v>-2.315154499287678</v>
       </c>
       <c r="G75">
-        <v>-8.465820898967714</v>
+        <v>-12.33193556954831</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.573105863467239</v>
       </c>
       <c r="E76">
-        <v>-18.03225424950474</v>
+        <v>-23.10465685565841</v>
       </c>
       <c r="F76">
-        <v>-0.1515764713465669</v>
+        <v>-2.228707733866327</v>
       </c>
       <c r="G76">
-        <v>-8.351477966586826</v>
+        <v>-12.17629027101948</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.40778823184368</v>
       </c>
       <c r="E77">
-        <v>-16.80857000315206</v>
+        <v>-24.32784296987025</v>
       </c>
       <c r="F77">
-        <v>-0.733841717346159</v>
+        <v>-2.261211214017374</v>
       </c>
       <c r="G77">
-        <v>-8.250450048364886</v>
+        <v>-11.71865700839832</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.231861659018109</v>
       </c>
       <c r="E78">
-        <v>-18.22381322850321</v>
+        <v>-23.94142828279574</v>
       </c>
       <c r="F78">
-        <v>-0.6699480828334275</v>
+        <v>-2.513164958150663</v>
       </c>
       <c r="G78">
-        <v>-7.550385535902906</v>
+        <v>-11.69490053360851</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.046571273783702</v>
       </c>
       <c r="E79">
-        <v>-18.12109385258722</v>
+        <v>-24.16129022434214</v>
       </c>
       <c r="F79">
-        <v>-0.7167359304783492</v>
+        <v>-2.379364570148279</v>
       </c>
       <c r="G79">
-        <v>-8.038114968021572</v>
+        <v>-11.39112156437945</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.856402798366334</v>
       </c>
       <c r="E80">
-        <v>-19.27714986810935</v>
+        <v>-24.09872029897816</v>
       </c>
       <c r="F80">
-        <v>-0.9486995124472808</v>
+        <v>-2.603479370975685</v>
       </c>
       <c r="G80">
-        <v>-7.757986536125062</v>
+        <v>-11.10230957153343</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.663834159340188</v>
       </c>
       <c r="E81">
-        <v>-20.31517573709557</v>
+        <v>-25.12602726998822</v>
       </c>
       <c r="F81">
-        <v>-1.190813080202715</v>
+        <v>-2.753387363125506</v>
       </c>
       <c r="G81">
-        <v>-6.58256410022467</v>
+        <v>-11.35926418465504</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.471736977928963</v>
       </c>
       <c r="E82">
-        <v>-21.48543304710576</v>
+        <v>-25.78890982370502</v>
       </c>
       <c r="F82">
-        <v>-1.291893784161922</v>
+        <v>-2.752244216109643</v>
       </c>
       <c r="G82">
-        <v>-7.455127898555916</v>
+        <v>-10.96634215569003</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.283053291311189</v>
       </c>
       <c r="E83">
-        <v>-20.93802205211055</v>
+        <v>-25.87241035593245</v>
       </c>
       <c r="F83">
-        <v>-1.682403573557067</v>
+        <v>-2.660568795641821</v>
       </c>
       <c r="G83">
-        <v>-7.097820718502377</v>
+        <v>-11.29744305725469</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.100940595970318</v>
       </c>
       <c r="E84">
-        <v>-20.50956048387482</v>
+        <v>-27.54938126503091</v>
       </c>
       <c r="F84">
-        <v>-1.254652042466861</v>
+        <v>-2.822962769654039</v>
       </c>
       <c r="G84">
-        <v>-6.374923373456042</v>
+        <v>-11.18289487105037</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.932669013687795</v>
       </c>
       <c r="E85">
-        <v>-23.82559897462755</v>
+        <v>-27.81390754571497</v>
       </c>
       <c r="F85">
-        <v>-1.400700670887039</v>
+        <v>-2.871698937430346</v>
       </c>
       <c r="G85">
-        <v>-6.437724422336016</v>
+        <v>-11.06710191972328</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.783862691916736</v>
       </c>
       <c r="E86">
-        <v>-23.1897876385286</v>
+        <v>-28.147493055016</v>
       </c>
       <c r="F86">
-        <v>-1.27102058234618</v>
+        <v>-2.936649568749049</v>
       </c>
       <c r="G86">
-        <v>-8.107143153060916</v>
+        <v>-10.8729781503915</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.66059200838983</v>
       </c>
       <c r="E87">
-        <v>-24.45248015998336</v>
+        <v>-29.00323425977146</v>
       </c>
       <c r="F87">
-        <v>-1.580581480772355</v>
+        <v>-3.100691993892838</v>
       </c>
       <c r="G87">
-        <v>-6.010637563405719</v>
+        <v>-10.56346531628842</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.568762429873416</v>
       </c>
       <c r="E88">
-        <v>-25.54233894246137</v>
+        <v>-30.18110846306255</v>
       </c>
       <c r="F88">
-        <v>-1.398250360109558</v>
+        <v>-3.176444536144047</v>
       </c>
       <c r="G88">
-        <v>-6.782382007884</v>
+        <v>-10.81271297939461</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.512396398031181</v>
       </c>
       <c r="E89">
-        <v>-26.58000706200098</v>
+        <v>-31.53720528939951</v>
       </c>
       <c r="F89">
-        <v>-1.514403208962702</v>
+        <v>-3.274676484605027</v>
       </c>
       <c r="G89">
-        <v>-6.758426900361834</v>
+        <v>-10.24066726293624</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.499988391648448</v>
       </c>
       <c r="E90">
-        <v>-27.65556039508876</v>
+        <v>-32.71193673172928</v>
       </c>
       <c r="F90">
-        <v>-1.706106478420772</v>
+        <v>-3.171823074403829</v>
       </c>
       <c r="G90">
-        <v>-6.322212867379766</v>
+        <v>-11.14953781419668</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.536670577392862</v>
       </c>
       <c r="E91">
-        <v>-29.86618026667312</v>
+        <v>-33.28107081653928</v>
       </c>
       <c r="F91">
-        <v>-1.792318815867131</v>
+        <v>-3.576581611494529</v>
       </c>
       <c r="G91">
-        <v>-6.957460208728357</v>
+        <v>-10.23240083072468</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.626588532234755</v>
       </c>
       <c r="E92">
-        <v>-30.71689033680606</v>
+        <v>-34.54544793032489</v>
       </c>
       <c r="F92">
-        <v>-1.865539038967982</v>
+        <v>-3.324066234262141</v>
       </c>
       <c r="G92">
-        <v>-6.709473863472631</v>
+        <v>-10.97140066927403</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.772779128509307</v>
       </c>
       <c r="E93">
-        <v>-31.75584907143785</v>
+        <v>-36.13517552342859</v>
       </c>
       <c r="F93">
-        <v>-1.862096344041947</v>
+        <v>-3.522151246191379</v>
       </c>
       <c r="G93">
-        <v>-6.185258908965657</v>
+        <v>-10.84037258737522</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.974017525731609</v>
       </c>
       <c r="E94">
-        <v>-33.7235208409847</v>
+        <v>-38.02680968591265</v>
       </c>
       <c r="F94">
-        <v>-1.662806057541637</v>
+        <v>-3.55492808758535</v>
       </c>
       <c r="G94">
-        <v>-6.606654940113946</v>
+        <v>-10.9376695207744</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.233256193350589</v>
       </c>
       <c r="E95">
-        <v>-35.91648419241317</v>
+        <v>-39.22935727983453</v>
       </c>
       <c r="F95">
-        <v>-1.566727864327936</v>
+        <v>-3.41042353600399</v>
       </c>
       <c r="G95">
-        <v>-6.675477871329855</v>
+        <v>-11.19541204373436</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.552795772264824</v>
       </c>
       <c r="E96">
-        <v>-37.84934784650006</v>
+        <v>-40.81361221209995</v>
       </c>
       <c r="F96">
-        <v>-2.475405486828854</v>
+        <v>-3.740961182171257</v>
       </c>
       <c r="G96">
-        <v>-6.767729533327186</v>
+        <v>-11.5453598810541</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.924774810182819</v>
       </c>
       <c r="E97">
-        <v>-38.24121708051681</v>
+        <v>-42.36069742971041</v>
       </c>
       <c r="F97">
-        <v>-2.027685331126763</v>
+        <v>-3.714250475267987</v>
       </c>
       <c r="G97">
-        <v>-6.640766801350597</v>
+        <v>-11.56805036018026</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.35392567813736</v>
       </c>
       <c r="E98">
-        <v>-40.93523117428695</v>
+        <v>-44.18275611754063</v>
       </c>
       <c r="F98">
-        <v>-1.646422607049068</v>
+        <v>-3.806971295398141</v>
       </c>
       <c r="G98">
-        <v>-6.742427033770536</v>
+        <v>-12.16461728744801</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.816182833062918</v>
       </c>
       <c r="E99">
-        <v>-44.0599982441407</v>
+        <v>-45.5667845715569</v>
       </c>
       <c r="F99">
-        <v>-2.48471633643632</v>
+        <v>-3.764434629264387</v>
       </c>
       <c r="G99">
-        <v>-6.550885489959384</v>
+        <v>-11.82875251085233</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.329288690267405</v>
       </c>
       <c r="E100">
-        <v>-44.34105798342676</v>
+        <v>-47.59407143717773</v>
       </c>
       <c r="F100">
-        <v>-2.229156708998644</v>
+        <v>-3.909514896190692</v>
       </c>
       <c r="G100">
-        <v>-6.888339328413914</v>
+        <v>-12.33477932816655</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.848707771689834</v>
       </c>
       <c r="E101">
-        <v>-47.24430116177329</v>
+        <v>-49.29372886893612</v>
       </c>
       <c r="F101">
-        <v>-2.261301506064279</v>
+        <v>-4.185268464173814</v>
       </c>
       <c r="G101">
-        <v>-7.615666183391793</v>
+        <v>-12.13025382475037</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.425375279116594</v>
       </c>
       <c r="E102">
-        <v>-49.37423381560748</v>
+        <v>-51.39463853285515</v>
       </c>
       <c r="F102">
-        <v>-2.339845646462923</v>
+        <v>-4.144893836961366</v>
       </c>
       <c r="G102">
-        <v>-8.225183964809169</v>
+        <v>-12.65756413933657</v>
       </c>
     </row>
   </sheetData>
